--- a/data/availability/projects/ilcazar/c-north.xlsx
+++ b/data/availability/projects/ilcazar/c-north.xlsx
@@ -461,12 +461,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C North latest availability</t>
+          <t>Updated inventory for c-north</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -582,17 +582,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C North</t>
+          <t>Launch Phase</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -632,17 +632,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>C North</t>
+          <t>Launch Phase</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Twin House</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -682,17 +682,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Q Villas</t>
+          <t>Launch Phase</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -732,17 +732,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Townhouses</t>
+          <t>Launch Phase</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
     </row>
@@ -782,17 +782,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Standalone Villas</t>
+          <t>Launch Phase</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
     </row>
@@ -885,17 +885,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CN-2BD-95</t>
+          <t>CN-2BR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C North</t>
+          <t>Launch Phase</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -909,10 +909,14 @@
       <c r="G2" t="n">
         <v>95</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>95 SQM</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -920,12 +924,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -942,17 +946,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chalet</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CN-3BD-120</t>
+          <t>CN-3BR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C North</t>
+          <t>Launch Phase</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -966,10 +970,14 @@
       <c r="G3" t="n">
         <v>120</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>120 SQM</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -977,12 +985,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -999,17 +1007,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Twin House</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CN-QV-155</t>
+          <t>CN-QVILLA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Q Villas</t>
+          <t>Launch Phase</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1023,10 +1031,14 @@
       <c r="G4" t="n">
         <v>155</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>155 SQM Q Villa</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1034,12 +1046,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1056,17 +1068,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CN-TH-160</t>
+          <t>CN-TH</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Townhouses</t>
+          <t>Launch Phase</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1080,10 +1092,14 @@
       <c r="G5" t="n">
         <v>160</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>160 SQM Townhouse</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1091,12 +1107,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1118,12 +1134,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CN-SA-180</t>
+          <t>CN-SA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Standalone Villas</t>
+          <t>Launch Phase</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1137,10 +1153,14 @@
       <c r="G6" t="n">
         <v>180</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>180 SQM Standalone</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1148,12 +1168,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Delivery 4 years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2.5%+2.5%+2.5%+2.5% over 10 years</t>
+          <t>2.5+2.5+2.5+2.5 over 10 years</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">

--- a/data/availability/projects/ilcazar/c-north.xlsx
+++ b/data/availability/projects/ilcazar/c-north.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
